--- a/results/0916-all/辽宁平源丘陵农林区/tech_selected_summary.xlsx
+++ b/results/0916-all/辽宁平源丘陵农林区/tech_selected_summary.xlsx
@@ -265,172 +265,172 @@
     <t>庄河市</t>
   </si>
   <si>
-    <t>县名</t>
-  </si>
-  <si>
-    <t>技术1</t>
-  </si>
-  <si>
-    <t>技术2</t>
-  </si>
-  <si>
-    <t>技术3</t>
-  </si>
-  <si>
-    <t>技术4</t>
-  </si>
-  <si>
-    <t>技术5</t>
-  </si>
-  <si>
-    <t>技术6</t>
-  </si>
-  <si>
-    <t>技术7</t>
-  </si>
-  <si>
-    <t>技术8</t>
-  </si>
-  <si>
-    <t>技术9</t>
-  </si>
-  <si>
-    <t>技术10</t>
-  </si>
-  <si>
-    <t>技术11</t>
-  </si>
-  <si>
-    <t>技术12</t>
-  </si>
-  <si>
-    <t>技术13</t>
-  </si>
-  <si>
-    <t>技术14</t>
-  </si>
-  <si>
-    <t>技术15</t>
-  </si>
-  <si>
-    <t>技术16</t>
-  </si>
-  <si>
-    <t>技术17</t>
-  </si>
-  <si>
-    <t>技术18</t>
-  </si>
-  <si>
-    <t>技术19</t>
-  </si>
-  <si>
-    <t>技术20</t>
-  </si>
-  <si>
-    <t>技术21</t>
-  </si>
-  <si>
-    <t>技术22</t>
-  </si>
-  <si>
-    <t>技术23</t>
-  </si>
-  <si>
-    <t>技术24</t>
-  </si>
-  <si>
-    <t>技术25</t>
-  </si>
-  <si>
-    <t>技术26</t>
-  </si>
-  <si>
-    <t>技术27</t>
-  </si>
-  <si>
-    <t>技术28</t>
-  </si>
-  <si>
-    <t>技术29</t>
-  </si>
-  <si>
-    <t>技术30</t>
-  </si>
-  <si>
-    <t>技术31</t>
-  </si>
-  <si>
-    <t>技术32</t>
-  </si>
-  <si>
-    <t>技术33</t>
-  </si>
-  <si>
-    <t>技术34</t>
-  </si>
-  <si>
-    <t>技术35</t>
-  </si>
-  <si>
-    <t>技术36</t>
-  </si>
-  <si>
-    <t>技术37</t>
-  </si>
-  <si>
-    <t>技术38</t>
-  </si>
-  <si>
-    <t>技术39</t>
-  </si>
-  <si>
-    <t>技术40</t>
-  </si>
-  <si>
-    <t>技术41</t>
-  </si>
-  <si>
-    <t>技术42</t>
-  </si>
-  <si>
-    <t>技术43</t>
-  </si>
-  <si>
-    <t>技术44</t>
-  </si>
-  <si>
-    <t>技术45</t>
-  </si>
-  <si>
-    <t>技术46</t>
-  </si>
-  <si>
-    <t>技术47</t>
-  </si>
-  <si>
-    <t>技术48</t>
-  </si>
-  <si>
-    <t>技术49</t>
-  </si>
-  <si>
-    <t>技术50</t>
-  </si>
-  <si>
-    <t>技术51</t>
-  </si>
-  <si>
-    <t>技术52</t>
-  </si>
-  <si>
-    <t>技术53</t>
-  </si>
-  <si>
-    <t>技术54</t>
-  </si>
-  <si>
-    <t>总经济成本</t>
+    <t>Counties</t>
+  </si>
+  <si>
+    <t>Tech1</t>
+  </si>
+  <si>
+    <t>Tech2</t>
+  </si>
+  <si>
+    <t>Tech3</t>
+  </si>
+  <si>
+    <t>Tech4</t>
+  </si>
+  <si>
+    <t>Tech5</t>
+  </si>
+  <si>
+    <t>Tech6</t>
+  </si>
+  <si>
+    <t>Tech7</t>
+  </si>
+  <si>
+    <t>Tech8</t>
+  </si>
+  <si>
+    <t>Tech9</t>
+  </si>
+  <si>
+    <t>Tech10</t>
+  </si>
+  <si>
+    <t>Tech11</t>
+  </si>
+  <si>
+    <t>Tech12</t>
+  </si>
+  <si>
+    <t>Tech13</t>
+  </si>
+  <si>
+    <t>Tech14</t>
+  </si>
+  <si>
+    <t>Tech15</t>
+  </si>
+  <si>
+    <t>Tech16</t>
+  </si>
+  <si>
+    <t>Tech17</t>
+  </si>
+  <si>
+    <t>Tech18</t>
+  </si>
+  <si>
+    <t>Tech19</t>
+  </si>
+  <si>
+    <t>Tech20</t>
+  </si>
+  <si>
+    <t>Tech21</t>
+  </si>
+  <si>
+    <t>Tech22</t>
+  </si>
+  <si>
+    <t>Tech23</t>
+  </si>
+  <si>
+    <t>Tech24</t>
+  </si>
+  <si>
+    <t>Tech25</t>
+  </si>
+  <si>
+    <t>Tech26</t>
+  </si>
+  <si>
+    <t>Tech27</t>
+  </si>
+  <si>
+    <t>Tech28</t>
+  </si>
+  <si>
+    <t>Tech29</t>
+  </si>
+  <si>
+    <t>Tech30</t>
+  </si>
+  <si>
+    <t>Tech31</t>
+  </si>
+  <si>
+    <t>Tech32</t>
+  </si>
+  <si>
+    <t>Tech33</t>
+  </si>
+  <si>
+    <t>Tech34</t>
+  </si>
+  <si>
+    <t>Tech35</t>
+  </si>
+  <si>
+    <t>Tech36</t>
+  </si>
+  <si>
+    <t>Tech37</t>
+  </si>
+  <si>
+    <t>Tech38</t>
+  </si>
+  <si>
+    <t>Tech39</t>
+  </si>
+  <si>
+    <t>Tech40</t>
+  </si>
+  <si>
+    <t>Tech41</t>
+  </si>
+  <si>
+    <t>Tech42</t>
+  </si>
+  <si>
+    <t>Tech43</t>
+  </si>
+  <si>
+    <t>Tech44</t>
+  </si>
+  <si>
+    <t>Tech45</t>
+  </si>
+  <si>
+    <t>Tech46</t>
+  </si>
+  <si>
+    <t>Tech47</t>
+  </si>
+  <si>
+    <t>Tech48</t>
+  </si>
+  <si>
+    <t>Tech49</t>
+  </si>
+  <si>
+    <t>Tech50</t>
+  </si>
+  <si>
+    <t>Tech51</t>
+  </si>
+  <si>
+    <t>Tech52</t>
+  </si>
+  <si>
+    <t>Tech53</t>
+  </si>
+  <si>
+    <t>Tech54</t>
+  </si>
+  <si>
+    <t>Total economic cost</t>
   </si>
   <si>
     <t>Feed processing_dairy</t>
@@ -544,10 +544,10 @@
     <t>irrigation (AWD irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 69949043.35</t>
-  </si>
-  <si>
-    <t>总经济成本: 0.00</t>
+    <t>69949043.35</t>
+  </si>
+  <si>
+    <t>0.00</t>
   </si>
   <si>
     <t>By-products source_sheep &amp; goat</t>
@@ -574,7 +574,7 @@
     <t>irrigation (drip irrigation)_friut</t>
   </si>
   <si>
-    <t>总经济成本: 449769929.13</t>
+    <t>449769929.13</t>
   </si>
   <si>
     <t>By-products source_beef cattle</t>
@@ -592,7 +592,7 @@
     <t>4R(Right rate)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 601840432.15</t>
+    <t>601840432.15</t>
   </si>
   <si>
     <t>EEF(CRF)_maize</t>
@@ -601,7 +601,7 @@
     <t>4R(Right type)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 390014858.91</t>
+    <t>390014858.91</t>
   </si>
   <si>
     <t>Probiotics_pig</t>
@@ -622,10 +622,10 @@
     <t>irrigation (water-saving irrigation)_rice</t>
   </si>
   <si>
-    <t>总经济成本: 634284054.52</t>
-  </si>
-  <si>
-    <t>总经济成本: 34291917.74</t>
+    <t>634284054.52</t>
+  </si>
+  <si>
+    <t>34291917.74</t>
   </si>
   <si>
     <t>nitrification inhibitor_poultry</t>
@@ -637,7 +637,7 @@
     <t>cover crop (mix)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 561308382.35</t>
+    <t>561308382.35</t>
   </si>
   <si>
     <t>Nitrocompounds_dairy</t>
@@ -661,10 +661,10 @@
     <t>4R(Right rate)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 258679930.73</t>
-  </si>
-  <si>
-    <t>总经济成本: 20218905.32</t>
+    <t>258679930.73</t>
+  </si>
+  <si>
+    <t>20218905.32</t>
   </si>
   <si>
     <t>Biochar_sheep &amp; goat</t>
@@ -673,16 +673,16 @@
     <t>Physical additives_pig</t>
   </si>
   <si>
-    <t>总经济成本: 903783793.25</t>
-  </si>
-  <si>
-    <t>总经济成本: 81100395.84</t>
-  </si>
-  <si>
-    <t>总经济成本: 3567.00</t>
-  </si>
-  <si>
-    <t>总经济成本: 310131309.13</t>
+    <t>903783793.25</t>
+  </si>
+  <si>
+    <t>81100395.84</t>
+  </si>
+  <si>
+    <t>3567.00</t>
+  </si>
+  <si>
+    <t>310131309.13</t>
   </si>
   <si>
     <t>Increasing feeding level_sheep &amp; goat</t>
@@ -691,13 +691,13 @@
     <t>chemical amendments_sheep&amp;goat</t>
   </si>
   <si>
-    <t>总经济成本: 1021041092.06</t>
-  </si>
-  <si>
-    <t>总经济成本: 17369393.31</t>
-  </si>
-  <si>
-    <t>总经济成本: 139674918.61</t>
+    <t>1021041092.06</t>
+  </si>
+  <si>
+    <t>17369393.31</t>
+  </si>
+  <si>
+    <t>139674918.61</t>
   </si>
   <si>
     <t>nitrification inhibitor_sheep&amp;goat</t>
@@ -712,28 +712,28 @@
     <t>EEF(DI)_wheat</t>
   </si>
   <si>
-    <t>总经济成本: 503697503.34</t>
-  </si>
-  <si>
-    <t>总经济成本: 31147537.85</t>
-  </si>
-  <si>
-    <t>总经济成本: 1301080.56</t>
+    <t>503697503.34</t>
+  </si>
+  <si>
+    <t>31147537.85</t>
+  </si>
+  <si>
+    <t>1301080.56</t>
   </si>
   <si>
     <t>Probiotics_poultry</t>
   </si>
   <si>
-    <t>总经济成本: 429877347.32</t>
+    <t>429877347.32</t>
   </si>
   <si>
     <t>surface crust cover_dairy</t>
   </si>
   <si>
-    <t>总经济成本: 194431901.66</t>
-  </si>
-  <si>
-    <t>总经济成本: 482.40</t>
+    <t>194431901.66</t>
+  </si>
+  <si>
+    <t>482.40</t>
   </si>
   <si>
     <t>surface crust cover_pig</t>
@@ -742,61 +742,61 @@
     <t>rolller press_pig</t>
   </si>
   <si>
-    <t>总经济成本: 73332931.44</t>
-  </si>
-  <si>
-    <t>总经济成本: 194971620.03</t>
+    <t>73332931.44</t>
+  </si>
+  <si>
+    <t>194971620.03</t>
   </si>
   <si>
     <t>irrigation (water-saving irrigation)_vegetable</t>
   </si>
   <si>
-    <t>总经济成本: 585304137.19</t>
-  </si>
-  <si>
-    <t>总经济成本: 696.80</t>
+    <t>585304137.19</t>
+  </si>
+  <si>
+    <t>696.80</t>
   </si>
   <si>
     <t>Screw press_pig</t>
   </si>
   <si>
-    <t>总经济成本: 205191861.38</t>
-  </si>
-  <si>
-    <t>总经济成本: 5319437.77</t>
+    <t>205191861.38</t>
+  </si>
+  <si>
+    <t>5319437.77</t>
   </si>
   <si>
     <t>manure（high）≥70%_rice</t>
   </si>
   <si>
-    <t>总经济成本: 427085786.63</t>
+    <t>427085786.63</t>
   </si>
   <si>
     <t>EEF(DI)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 807159681.06</t>
+    <t>807159681.06</t>
   </si>
   <si>
     <t>artificial film cover_pig</t>
   </si>
   <si>
-    <t>总经济成本: 234542.80</t>
-  </si>
-  <si>
-    <t>总经济成本: 4107329.07</t>
-  </si>
-  <si>
-    <t>总经济成本: 12719871.49</t>
-  </si>
-  <si>
-    <t>总经济成本: 649576994.89</t>
-  </si>
-  <si>
-    <t>总经济成本: 5309795.41</t>
-  </si>
-  <si>
-    <t>总经济成本: 222395047.60</t>
+    <t>234542.80</t>
+  </si>
+  <si>
+    <t>4107329.07</t>
+  </si>
+  <si>
+    <t>12719871.49</t>
+  </si>
+  <si>
+    <t>649576994.89</t>
+  </si>
+  <si>
+    <t>5309795.41</t>
+  </si>
+  <si>
+    <t>222395047.60</t>
   </si>
   <si>
     <t>Yucca extract_Beef cattle</t>
@@ -811,31 +811,31 @@
     <t>tillage management (zero tillage)_maize</t>
   </si>
   <si>
-    <t>总经济成本: 209447984.40</t>
-  </si>
-  <si>
-    <t>总经济成本: 4654637.19</t>
-  </si>
-  <si>
-    <t>总经济成本: 44533484.89</t>
+    <t>209447984.40</t>
+  </si>
+  <si>
+    <t>4654637.19</t>
+  </si>
+  <si>
+    <t>44533484.89</t>
   </si>
   <si>
     <t>Organic acid_sheep &amp; goat</t>
   </si>
   <si>
-    <t>总经济成本: 550713022.90</t>
+    <t>550713022.90</t>
   </si>
   <si>
     <t>residue rerention_rice</t>
   </si>
   <si>
-    <t>总经济成本: 55984139.54</t>
-  </si>
-  <si>
-    <t>总经济成本: 3234.40</t>
-  </si>
-  <si>
-    <t>总经济成本: 516911319.48</t>
+    <t>55984139.54</t>
+  </si>
+  <si>
+    <t>3234.40</t>
+  </si>
+  <si>
+    <t>516911319.48</t>
   </si>
 </sst>
 </file>
